--- a/jogos_2025-10-13.xlsx
+++ b/jogos_2025-10-13.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>5.1</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z5" t="n">
         <v>1.98</v>
       </c>
-      <c r="M5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>2.04</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.92</v>
+        <v>3.78</v>
       </c>
       <c r="R6" t="n">
         <v>1.41</v>
@@ -1323,34 +1323,34 @@
         <v>1.63</v>
       </c>
       <c r="O7" t="n">
-        <v>2.15</v>
+        <v>4.48</v>
       </c>
       <c r="P7" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>2.21</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="T7" t="n">
         <v>2.63</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="V7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="X7" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="Y7" t="n">
         <v>2.05</v>
@@ -1359,16 +1359,16 @@
         <v>1.77</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.25</v>
+        <v>1.18</v>
       </c>
       <c r="AI7" t="n">
         <v>1.48</v>
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>

--- a/jogos_2025-10-13.xlsx
+++ b/jogos_2025-10-13.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="P3" t="n">
         <v>1.98</v>
       </c>
-      <c r="M3" t="n">
+      <c r="Q3" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA3" t="n">
         <v>3.5</v>
       </c>
-      <c r="N3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N4" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1056,16 +1056,16 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N5" t="n">
-        <v>5.1</v>
+        <v>4.85</v>
       </c>
       <c r="O5" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="P5" t="n">
         <v>2.3</v>
@@ -1080,7 +1080,7 @@
         <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
       <c r="U5" t="n">
         <v>1.44</v>
@@ -1089,22 +1089,22 @@
         <v>1.05</v>
       </c>
       <c r="W5" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X5" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AC5" t="n">
         <v>1.75</v>
@@ -1185,28 +1185,28 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="P6" t="n">
         <v>2.04</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.78</v>
+        <v>3.92</v>
       </c>
       <c r="R6" t="n">
         <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T6" t="n">
         <v>2.91</v>
@@ -1215,16 +1215,16 @@
         <v>1.34</v>
       </c>
       <c r="V6" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
         <v>1.3</v>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="Y6" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Z6" t="n">
         <v>1.72</v>
@@ -1236,10 +1236,10 @@
         <v>1.23</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1323,28 +1323,28 @@
         <v>1.63</v>
       </c>
       <c r="O7" t="n">
-        <v>4.48</v>
+        <v>5.5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
         <v>2.8</v>
       </c>
       <c r="T7" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="U7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W7" t="n">
         <v>1.34</v>
@@ -1359,16 +1359,16 @@
         <v>1.77</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.15</v>
+        <v>3.38</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AI7" t="n">
         <v>1.48</v>
@@ -1581,34 +1581,34 @@
         <v>2.68</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Y9" t="n">
         <v>2.2</v>
@@ -1617,16 +1617,16 @@
         <v>1.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1710,34 +1710,34 @@
         <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y10" t="n">
         <v>2.05</v>
@@ -1746,16 +1746,16 @@
         <v>1.68</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1968,34 +1968,34 @@
         <v>4.7</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y12" t="n">
         <v>1.92</v>
@@ -2004,16 +2004,16 @@
         <v>1.78</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>

--- a/jogos_2025-10-13.xlsx
+++ b/jogos_2025-10-13.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y4" t="n">
         <v>1.85</v>
       </c>
-      <c r="M4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.14</v>
-      </c>
       <c r="Z4" t="n">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.58</v>
+        <v>3.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,77 +1056,77 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>4.85</v>
+        <v>3.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.5</v>
+        <v>4.69</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="T5" t="n">
-        <v>2.63</v>
+        <v>2.99</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="V5" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
         <v>1.24</v>
       </c>
-      <c r="X5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH5" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="M6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X6" t="n">
         <v>3.1</v>
       </c>
-      <c r="N6" t="n">
-        <v>3</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.97</v>
-      </c>
       <c r="Y6" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.62</v>
+        <v>1.14</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45943.65625</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="M7" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>1.63</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>5.5</v>
+        <v>2.77</v>
       </c>
       <c r="P7" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.3</v>
+        <v>3.92</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="T7" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="X7" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.38</v>
+        <v>3.55</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.14</v>
+        <v>1.62</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45943.65625</v>
@@ -1572,19 +1572,19 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.45</v>
+        <v>2.61</v>
       </c>
       <c r="M9" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="O9" t="n">
         <v>3.28</v>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q9" t="n">
         <v>3.48</v>
@@ -1596,25 +1596,25 @@
         <v>2.41</v>
       </c>
       <c r="T9" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="U9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V9" t="n">
         <v>1.04</v>
       </c>
       <c r="W9" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="X9" t="n">
         <v>2.52</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AA9" t="n">
         <v>4.45</v>
@@ -1701,22 +1701,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="O10" t="n">
-        <v>2.82</v>
+        <v>2.87</v>
       </c>
       <c r="P10" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.74</v>
+        <v>3.82</v>
       </c>
       <c r="R10" t="n">
         <v>1.4</v>
@@ -1725,7 +1725,7 @@
         <v>2.66</v>
       </c>
       <c r="T10" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="U10" t="n">
         <v>1.33</v>
@@ -1734,28 +1734,28 @@
         <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X10" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AB10" t="n">
         <v>1.22</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
         <v>1.9</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1962,10 +1962,10 @@
         <v>1.66</v>
       </c>
       <c r="M12" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
         <v>2.19</v>
@@ -1989,19 +1989,19 @@
         <v>1.34</v>
       </c>
       <c r="V12" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="X12" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AA12" t="n">
         <v>3.5</v>
@@ -2010,7 +2010,7 @@
         <v>1.22</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AD12" t="n">
         <v>1.73</v>

--- a/jogos_2025-10-13.xlsx
+++ b/jogos_2025-10-13.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="M3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S3" t="n">
         <v>3</v>
       </c>
-      <c r="N3" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O3" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="T3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1.98</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AA3" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AC3" t="n">
         <v>1.85</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,77 +927,77 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="M4" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>4.85</v>
+        <v>3.45</v>
       </c>
       <c r="O4" t="n">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.5</v>
+        <v>4.69</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="T4" t="n">
-        <v>2.63</v>
+        <v>2.99</v>
       </c>
       <c r="U4" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
         <v>1.24</v>
       </c>
-      <c r="X4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH4" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N5" t="n">
         <v>3.2</v>
       </c>
-      <c r="N5" t="n">
-        <v>3.5</v>
-      </c>
       <c r="O5" t="n">
-        <v>2.49</v>
+        <v>3.04</v>
       </c>
       <c r="P5" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.69</v>
+        <v>3.71</v>
       </c>
       <c r="R5" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="T5" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="X5" t="n">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.58</v>
+        <v>3.82</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AC5" t="n">
         <v>1.86</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1185,16 +1185,16 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="O6" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
         <v>2.08</v>
@@ -1218,7 +1218,7 @@
         <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X6" t="n">
         <v>3.1</v>
@@ -1230,13 +1230,13 @@
         <v>1.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="AB6" t="n">
         <v>1.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AD6" t="n">
         <v>1.8</v>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AI6" t="n">
         <v>1.48</v>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="O7" t="n">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="P7" t="n">
         <v>2.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.92</v>
+        <v>3.84</v>
       </c>
       <c r="R7" t="n">
         <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="T7" t="n">
         <v>2.91</v>
@@ -1359,7 +1359,7 @@
         <v>1.72</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="AB7" t="n">
         <v>1.23</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>

--- a/jogos_2025-10-13.xlsx
+++ b/jogos_2025-10-13.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>5.1</v>
+        <v>3.2</v>
       </c>
       <c r="O3" t="n">
-        <v>2.1</v>
+        <v>3.04</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.5</v>
+        <v>3.71</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="T3" t="n">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W3" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="X3" t="n">
-        <v>3.5</v>
+        <v>2.74</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.2</v>
+        <v>3.82</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA5" t="n">
         <v>3.2</v>
       </c>
-      <c r="O5" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.82</v>
-      </c>
       <c r="AB5" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.4</v>
+        <v>2.27</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>3.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.69</v>
+        <v>2.89</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>2.81</v>
       </c>
       <c r="P6" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.3</v>
+        <v>3.69</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S6" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T6" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="U6" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="X6" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.75</v>
+        <v>3.14</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45943.65625</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.27</v>
+        <v>4.6</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N7" t="n">
-        <v>2.92</v>
+        <v>1.63</v>
       </c>
       <c r="O7" t="n">
-        <v>2.82</v>
+        <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.84</v>
+        <v>2.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="T7" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="U7" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
         <v>1.3</v>
       </c>
-      <c r="X7" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.58</v>
+        <v>1.18</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45943.65625</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>2.8</v>
+        <v>3.26</v>
       </c>
       <c r="O10" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,62 +1830,62 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.26</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y11" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.9</v>
       </c>
-      <c r="Z11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
       <c r="AE11" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>

--- a/jogos_2025-10-13.xlsx
+++ b/jogos_2025-10-13.xlsx
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.15</v>
+        <v>2.41</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>3.11</v>
       </c>
       <c r="N3" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="O3" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="P3" t="n">
         <v>1.98</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.71</v>
+        <v>3.67</v>
       </c>
       <c r="R3" t="n">
         <v>1.44</v>
@@ -831,10 +831,10 @@
         <v>1.03</v>
       </c>
       <c r="W3" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="X3" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="Y3" t="n">
         <v>2.17</v>
@@ -843,16 +843,16 @@
         <v>1.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>1.28</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z4" t="n">
         <v>1.98</v>
       </c>
-      <c r="M4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AA4" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>3.23</v>
       </c>
       <c r="N5" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P5" t="n">
         <v>2.1</v>
       </c>
-      <c r="P5" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Q5" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X5" t="n">
         <v>3</v>
       </c>
-      <c r="T5" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W5" t="n">
+      <c r="Y5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1.25</v>
       </c>
-      <c r="X5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AC5" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.27</v>
+        <v>4.6</v>
       </c>
       <c r="M6" t="n">
-        <v>3.01</v>
+        <v>3.45</v>
       </c>
       <c r="N6" t="n">
-        <v>2.89</v>
+        <v>1.63</v>
       </c>
       <c r="O6" t="n">
-        <v>2.81</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.69</v>
+        <v>2.3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="T6" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="U6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="X6" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.14</v>
+        <v>3.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45943.65625</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.6</v>
+        <v>2.27</v>
       </c>
       <c r="M7" t="n">
-        <v>3.45</v>
+        <v>3.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.63</v>
+        <v>2.89</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>2.81</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.3</v>
+        <v>3.69</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S7" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="T7" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="X7" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.75</v>
+        <v>3.14</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45943.65625</v>
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="M8" t="n">
         <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1572,22 +1572,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="N9" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="O9" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
         <v>1.49</v>
@@ -1611,22 +1611,22 @@
         <v>2.52</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.09</v>
+        <v>2.31</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>3.26</v>
+        <v>2.75</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="N11" t="n">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="O11" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1962,22 +1962,22 @@
         <v>1.66</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O12" t="n">
         <v>2.19</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.98</v>
+        <v>6.09</v>
       </c>
       <c r="R12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
         <v>2.69</v>
@@ -1989,7 +1989,7 @@
         <v>1.34</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
         <v>1.28</v>
@@ -1998,10 +1998,10 @@
         <v>3.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AA12" t="n">
         <v>3.5</v>
@@ -2010,7 +2010,7 @@
         <v>1.22</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AD12" t="n">
         <v>1.73</v>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>

--- a/jogos_2025-10-13.xlsx
+++ b/jogos_2025-10-13.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.41</v>
+        <v>1.6</v>
       </c>
       <c r="M3" t="n">
-        <v>3.11</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>2.75</v>
+        <v>5.1</v>
       </c>
       <c r="O3" t="n">
-        <v>3.06</v>
+        <v>2.1</v>
       </c>
       <c r="P3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1.98</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U3" t="n">
+      <c r="AA3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB3" t="n">
         <v>1.3</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.19</v>
       </c>
       <c r="AC3" t="n">
         <v>1.85</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.47</v>
+        <v>2.3</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45943.64583333334</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.6</v>
+        <v>2.41</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>3.11</v>
       </c>
       <c r="N4" t="n">
-        <v>5.1</v>
+        <v>2.75</v>
       </c>
       <c r="O4" t="n">
-        <v>2.1</v>
+        <v>3.06</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.5</v>
+        <v>3.67</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="T4" t="n">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="X4" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AC4" t="n">
         <v>1.85</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.3</v>
+        <v>1.47</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45943.64583333334</v>
@@ -1065,34 +1065,34 @@
         <v>4.3</v>
       </c>
       <c r="O5" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.33</v>
+        <v>5.01</v>
       </c>
       <c r="R5" t="n">
         <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="T5" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="U5" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="Y5" t="n">
         <v>1.8</v>
@@ -1101,17 +1101,17 @@
         <v>1.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.83</v>
       </c>
-      <c r="AD5" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45943.64583333334</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.6</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>1.63</v>
+        <v>2.9</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>2.83</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.3</v>
+        <v>3.68</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="T6" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="U6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="X6" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.75</v>
+        <v>3.14</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.18</v>
+        <v>1.56</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="AJ6" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45943.65625</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.27</v>
+        <v>4.75</v>
       </c>
       <c r="M7" t="n">
-        <v>3.01</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>2.89</v>
+        <v>1.7</v>
       </c>
       <c r="O7" t="n">
-        <v>2.81</v>
+        <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.69</v>
+        <v>2.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T7" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="U7" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="X7" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.14</v>
+        <v>3.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45943.65625</v>
@@ -1452,13 +1452,13 @@
         <v>4.45</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1494,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1516,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45943.66666666666</v>
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.31</v>
+        <v>2.48</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S10" t="n">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="T10" t="n">
-        <v>2.95</v>
+        <v>3.12</v>
       </c>
       <c r="U10" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
         <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="X10" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="M11" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>2.93</v>
+        <v>3.35</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>

--- a/jogos_2025-10-13.xlsx
+++ b/jogos_2025-10-13.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="N3" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="O3" t="n">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.5</v>
+        <v>5.01</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="T3" t="n">
-        <v>2.63</v>
+        <v>2.94</v>
       </c>
       <c r="U3" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X3" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA3" t="n">
         <v>3.5</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AB3" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45943.64583333334</v>
@@ -927,31 +927,31 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="M4" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O4" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.67</v>
+        <v>3.55</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="T4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U4" t="n">
         <v>1.3</v>
@@ -960,28 +960,28 @@
         <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X4" t="n">
         <v>2.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" t="n">
         <v>1.85</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AI4" t="n">
         <v>1.9</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="M5" t="n">
-        <v>3.23</v>
+        <v>4.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="O5" t="n">
-        <v>2.41</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.01</v>
+        <v>4.84</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="U5" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1.3</v>
       </c>
-      <c r="X5" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AC5" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1126,13 +1126,13 @@
         <v>1.24</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.84</v>
+        <v>2.57</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45943.64583333334</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="O6" t="n">
         <v>2.83</v>
@@ -1224,22 +1224,22 @@
         <v>3.14</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="X7" t="n">
         <v>3.1</v>
@@ -1356,7 +1356,7 @@
         <v>2.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AA7" t="n">
         <v>3.75</v>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.45</v>
+        <v>2.61</v>
       </c>
       <c r="M9" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="O9" t="n">
         <v>3.3</v>
@@ -1611,10 +1611,10 @@
         <v>2.52</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AA9" t="n">
         <v>4.5</v>
@@ -1645,10 +1645,10 @@
         <v>1.45</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45943.79166666666</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.48</v>
+        <v>2.08</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>2.78</v>
+        <v>3.35</v>
       </c>
       <c r="O10" t="n">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
       <c r="P10" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45943.83333333334</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.08</v>
+        <v>2.48</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="N11" t="n">
-        <v>3.35</v>
+        <v>2.78</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45943.83333333334</v>
@@ -1959,22 +1959,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="M12" t="n">
-        <v>3.29</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O12" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="P12" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.09</v>
+        <v>6.24</v>
       </c>
       <c r="R12" t="n">
         <v>1.4</v>
@@ -1983,28 +1983,28 @@
         <v>2.69</v>
       </c>
       <c r="T12" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="U12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W12" t="n">
         <v>1.28</v>
       </c>
       <c r="X12" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="AB12" t="n">
         <v>1.22</v>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45943.89583333334</v>

--- a/jogos_2025-10-13.xlsx
+++ b/jogos_2025-10-13.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="M3" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="N3" t="n">
-        <v>3.95</v>
+        <v>5.7</v>
       </c>
       <c r="O3" t="n">
-        <v>2.41</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.01</v>
+        <v>4.84</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AA3" t="n">
         <v>2.94</v>
       </c>
-      <c r="U3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W3" t="n">
+      <c r="AB3" t="n">
         <v>1.3</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.22</v>
       </c>
       <c r="AC3" t="n">
         <v>1.86</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.84</v>
+        <v>2.54</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45943.64583333334</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -960,16 +960,16 @@
         <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="X4" t="n">
         <v>2.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AA4" t="n">
         <v>4</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
-        <v>4.05</v>
+        <v>3.23</v>
       </c>
       <c r="N5" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>2.41</v>
       </c>
       <c r="P5" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.84</v>
+        <v>5.01</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="T5" t="n">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X5" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA5" t="n">
         <v>3.5</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AB5" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1126,13 +1126,13 @@
         <v>1.24</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.57</v>
+        <v>1.84</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45943.64583333334</v>
@@ -1572,28 +1572,28 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="R9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S9" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="T9" t="n">
         <v>3.35</v>
@@ -1605,28 +1605,28 @@
         <v>1.04</v>
       </c>
       <c r="W9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X9" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" t="n">
         <v>2.05</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.08</v>
+        <v>2.48</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
         <v>3.35</v>
       </c>
-      <c r="O10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>2.1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>2.37</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45943.83333333334</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="O11" t="n">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
       <c r="P11" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45943.83333333334</v>
@@ -1962,19 +1962,19 @@
         <v>1.57</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.24</v>
+        <v>6.3</v>
       </c>
       <c r="R12" t="n">
         <v>1.4</v>
@@ -1983,37 +1983,37 @@
         <v>2.69</v>
       </c>
       <c r="T12" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="U12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
         <v>1.28</v>
       </c>
       <c r="X12" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AB12" t="n">
         <v>1.22</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AH12" t="n">
         <v>2.25</v>

--- a/jogos_2025-10-13.xlsx
+++ b/jogos_2025-10-13.xlsx
@@ -669,22 +669,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="M2" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -742,10 +742,10 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45943.54166666666</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="M3" t="n">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="N3" t="n">
-        <v>5.7</v>
+        <v>4.09</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>2.41</v>
       </c>
       <c r="P3" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.84</v>
+        <v>5.01</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="T3" t="n">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="U3" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="X3" t="n">
-        <v>3.76</v>
+        <v>2.97</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.88</v>
+        <v>2.01</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.01</v>
+        <v>1.72</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AC3" t="n">
         <v>1.86</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.54</v>
+        <v>1.84</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45943.64583333334</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.41</v>
+        <v>1.6</v>
       </c>
       <c r="M4" t="n">
-        <v>3.11</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>2.75</v>
+        <v>5.1</v>
       </c>
       <c r="O4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S4" t="n">
         <v>3</v>
       </c>
-      <c r="P4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.55</v>
-      </c>
       <c r="T4" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="U4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1.3</v>
       </c>
-      <c r="V4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AC4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.55</v>
+        <v>2.54</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.2</v>
+        <v>2.87</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45943.64583333334</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="O5" t="n">
-        <v>2.41</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.01</v>
+        <v>3.55</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S5" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="T5" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="U5" t="n">
         <v>1.33</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="X5" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.8</v>
+        <v>2.13</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AB5" t="n">
         <v>1.22</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45943.64583333334</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.22</v>
+        <v>4.6</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N6" t="n">
-        <v>2.98</v>
+        <v>1.63</v>
       </c>
       <c r="O6" t="n">
-        <v>2.83</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.68</v>
+        <v>2.3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="T6" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="U6" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="X6" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AA6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>3.2</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45943.65625</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.75</v>
+        <v>2.27</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6</v>
+        <v>3.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.7</v>
+        <v>2.89</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>2.71</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.3</v>
+        <v>3.21</v>
       </c>
       <c r="R7" t="n">
         <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="X7" t="n">
-        <v>3.1</v>
+        <v>3.61</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AB7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
         <v>1.25</v>
       </c>
-      <c r="AC7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45943.65625</v>
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N8" t="n">
-        <v>4.45</v>
+        <v>4.78</v>
       </c>
       <c r="O8" t="n">
         <v>2.3</v>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="N9" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="O9" t="n">
         <v>3.32</v>
@@ -1611,10 +1611,10 @@
         <v>2.56</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AA9" t="n">
         <v>4.4</v>
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.48</v>
+        <v>2.31</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="O10" t="n">
         <v>3.1</v>
@@ -1740,10 +1740,10 @@
         <v>2.88</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AA10" t="n">
         <v>3.9</v>
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="N11" t="n">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="O11" t="n">
         <v>2.62</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="N12" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="O12" t="n">
         <v>2.06</v>
@@ -1998,10 +1998,10 @@
         <v>3.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AA12" t="n">
         <v>3.5</v>

--- a/jogos_2025-10-13.xlsx
+++ b/jogos_2025-10-13.xlsx
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.15</v>
+        <v>3.23</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="N2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="O2" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI2" t="n">
         <v>2.3</v>
@@ -798,77 +798,77 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="M3" t="n">
-        <v>3.35</v>
+        <v>3.23</v>
       </c>
       <c r="N3" t="n">
-        <v>4.09</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="P3" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.01</v>
+        <v>3.86</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="T3" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X3" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AA3" t="n">
         <v>3.35</v>
       </c>
       <c r="AB3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC3" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH3" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AI3" t="n">
         <v>1.61</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.6</v>
+        <v>2.41</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>3.11</v>
       </c>
       <c r="N4" t="n">
-        <v>5.1</v>
+        <v>2.75</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.84</v>
+        <v>3.21</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="T4" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
         <v>1.28</v>
       </c>
-      <c r="X4" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH4" t="n">
-        <v>2.54</v>
+        <v>1.42</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.87</v>
+        <v>2.2</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45943.64583333334</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="O5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>2.55</v>
       </c>
-      <c r="T5" t="n">
-        <v>3.1</v>
-      </c>
       <c r="U5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1.33</v>
       </c>
-      <c r="V5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AC5" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.55</v>
+        <v>2.34</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.2</v>
+        <v>2.87</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45943.64583333334</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.6</v>
+        <v>2.27</v>
       </c>
       <c r="M6" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA6" t="n">
         <v>3.45</v>
       </c>
-      <c r="N6" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="O6" t="n">
-        <v>5</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AB6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
         <v>1.28</v>
       </c>
-      <c r="AC6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH6" t="n">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="AJ6" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45943.65625</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q7" t="n">
         <v>2.27</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.21</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T7" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="U7" t="n">
         <v>1.4</v>
@@ -1347,28 +1347,28 @@
         <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="X7" t="n">
-        <v>3.61</v>
+        <v>3.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.01</v>
+        <v>1.79</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.47</v>
+        <v>1.18</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.9</v>
+        <v>1.48</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45943.65625</v>
@@ -1446,10 +1446,10 @@
         <v>1.65</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N8" t="n">
-        <v>4.78</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
         <v>2.3</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Z8" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1581,34 +1581,34 @@
         <v>2.68</v>
       </c>
       <c r="O9" t="n">
-        <v>3.32</v>
+        <v>3.09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="Q9" t="n">
         <v>3.44</v>
       </c>
       <c r="R9" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="T9" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="X9" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="Y9" t="n">
         <v>2.2</v>
@@ -1617,16 +1617,16 @@
         <v>1.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.4</v>
+        <v>4.83</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AC9" t="n">
         <v>1.95</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH9" t="n">
         <v>1.44</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.31</v>
+        <v>2.16</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="N10" t="n">
-        <v>2.75</v>
+        <v>2.93</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45943.83333333334</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.16</v>
+        <v>2.31</v>
       </c>
       <c r="M11" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="O11" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>2.1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>2.37</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45943.83333333334</v>
@@ -1971,10 +1971,10 @@
         <v>2.06</v>
       </c>
       <c r="P12" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="R12" t="n">
         <v>1.4</v>
@@ -1983,10 +1983,10 @@
         <v>2.69</v>
       </c>
       <c r="T12" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="U12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V12" t="n">
         <v>1.01</v>
@@ -1995,7 +1995,7 @@
         <v>1.28</v>
       </c>
       <c r="X12" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="Y12" t="n">
         <v>1.92</v>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AI12" t="n">
         <v>1.5</v>

--- a/jogos_2025-10-13.xlsx
+++ b/jogos_2025-10-13.xlsx
@@ -669,22 +669,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.23</v>
+        <v>2.67</v>
       </c>
       <c r="M2" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="O2" t="n">
-        <v>4.1</v>
+        <v>3.42</v>
       </c>
       <c r="P2" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="R2" t="n">
         <v>1.41</v>
@@ -693,37 +693,37 @@
         <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="U2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.32</v>
       </c>
-      <c r="V2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.31</v>
-      </c>
       <c r="X2" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.97</v>
+        <v>2.09</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AI2" t="n">
         <v>2.3</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.8</v>
+        <v>2.37</v>
       </c>
       <c r="M3" t="n">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>2.82</v>
       </c>
       <c r="O3" t="n">
-        <v>2.47</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.86</v>
+        <v>3.48</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X3" t="n">
         <v>2.7</v>
       </c>
-      <c r="T3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3</v>
-      </c>
       <c r="Y3" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="Z3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI3" t="n">
         <v>1.9</v>
       </c>
-      <c r="AA3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AJ3" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45943.64583333334</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.41</v>
+        <v>1.52</v>
       </c>
       <c r="M4" t="n">
-        <v>3.11</v>
+        <v>3.6</v>
       </c>
       <c r="N4" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.21</v>
+        <v>5.68</v>
       </c>
       <c r="R4" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
         <v>2.55</v>
       </c>
-      <c r="T4" t="n">
-        <v>3.1</v>
-      </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="X4" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.2</v>
+        <v>2.87</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45943.64583333334</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="N5" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="O5" t="n">
-        <v>2.1</v>
+        <v>2.64</v>
       </c>
       <c r="P5" t="n">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.8</v>
+        <v>4.47</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="T5" t="n">
-        <v>2.55</v>
+        <v>2.99</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="V5" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="X5" t="n">
-        <v>3.6</v>
+        <v>2.92</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.99</v>
+        <v>3.35</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AD5" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.34</v>
+        <v>1.68</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45943.64583333334</v>
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>3.01</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="O6" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="P6" t="n">
         <v>2.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="R6" t="n">
         <v>1.38</v>
@@ -1212,31 +1212,31 @@
         <v>2.86</v>
       </c>
       <c r="U6" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="V6" t="n">
         <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X6" t="n">
         <v>3.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AB6" t="n">
         <v>1.24</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AD6" t="n">
         <v>2</v>
@@ -1255,7 +1255,7 @@
         <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AI6" t="n">
         <v>1.9</v>
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.6</v>
+        <v>5.04</v>
       </c>
       <c r="M7" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="O7" t="n">
         <v>5</v>
@@ -1335,7 +1335,7 @@
         <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="T7" t="n">
         <v>2.8</v>
@@ -1344,28 +1344,28 @@
         <v>1.4</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W7" t="n">
         <v>1.33</v>
       </c>
       <c r="X7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="n">
         <v>2.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AD7" t="n">
         <v>1.79</v>
@@ -1446,10 +1446,10 @@
         <v>1.65</v>
       </c>
       <c r="M8" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
         <v>2.3</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1572,19 +1572,19 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="M9" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
-        <v>3.09</v>
+        <v>3.19</v>
       </c>
       <c r="P9" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q9" t="n">
         <v>3.44</v>
@@ -1593,40 +1593,40 @@
         <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="T9" t="n">
         <v>3.3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V9" t="n">
         <v>1.1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X9" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.83</v>
+        <v>4.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AC9" t="n">
         <v>1.95</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
         <v>1.44</v>
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.93</v>
+        <v>3.37</v>
       </c>
       <c r="O10" t="n">
         <v>2.62</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P11" t="n">
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="R11" t="n">
         <v>1.46</v>
@@ -1854,7 +1854,7 @@
         <v>2.55</v>
       </c>
       <c r="T11" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
         <v>1.31</v>
@@ -1869,22 +1869,22 @@
         <v>2.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="AB11" t="n">
         <v>1.22</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AH11" t="n">
         <v>1.5</v>
@@ -1959,16 +1959,16 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="P12" t="n">
         <v>2.1</v>
@@ -1980,40 +1980,40 @@
         <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="T12" t="n">
         <v>2.8</v>
       </c>
       <c r="U12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W12" t="n">
         <v>1.35</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.28</v>
-      </c>
       <c r="X12" t="n">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AA12" t="n">
         <v>3.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="AI12" t="n">
         <v>1.5</v>

--- a/jogos_2025-10-13.xlsx
+++ b/jogos_2025-10-13.xlsx
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="P2" t="n">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="S2" t="n">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="T2" t="n">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="U2" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="V2" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="W2" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="X2" t="n">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.09</v>
+        <v>2.34</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.74</v>
+        <v>4.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="AH2" t="n">
         <v>1.36</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.37</v>
+        <v>1.6</v>
       </c>
       <c r="M3" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S3" t="n">
         <v>3.1</v>
       </c>
-      <c r="N3" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="O3" t="n">
+      <c r="T3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AA3" t="n">
         <v>3</v>
       </c>
-      <c r="P3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>4</v>
-      </c>
       <c r="AB3" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.44</v>
+        <v>2.4</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.2</v>
+        <v>2.87</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45943.64583333334</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.52</v>
+        <v>2.55</v>
       </c>
       <c r="M4" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>2.15</v>
+        <v>3.21</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.68</v>
+        <v>3.09</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="T4" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
         <v>1.28</v>
       </c>
-      <c r="X4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH4" t="n">
-        <v>2.1</v>
+        <v>1.34</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.87</v>
+        <v>2.2</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45943.64583333334</v>
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="M5" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="N5" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="P5" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.47</v>
+        <v>3.43</v>
       </c>
       <c r="R5" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="T5" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="X5" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AI5" t="n">
         <v>1.61</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>6.57</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>2.9</v>
+        <v>1.66</v>
       </c>
       <c r="O6" t="n">
-        <v>2.78</v>
+        <v>6</v>
       </c>
       <c r="P6" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.28</v>
+        <v>2.05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="T6" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="U6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X6" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.56</v>
+        <v>1.13</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.9</v>
+        <v>1.48</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45943.65625</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5.04</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>1.66</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>2.85</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.27</v>
+        <v>3.68</v>
       </c>
       <c r="R7" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="T7" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.8</v>
+        <v>3.19</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.18</v>
+        <v>1.56</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45943.65625</v>
@@ -1443,77 +1443,77 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="M8" t="n">
         <v>3.6</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>4.53</v>
       </c>
       <c r="O8" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="P8" t="n">
         <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y8" t="n">
         <v>1.8</v>
       </c>
       <c r="Z8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH8" t="n">
         <v>2</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>1.57</v>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="O9" t="n">
         <v>3.19</v>
@@ -1611,10 +1611,10 @@
         <v>2.56</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AA9" t="n">
         <v>4.6</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y10" t="n">
         <v>2</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P10" t="n">
+      <c r="Z10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>2.1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>2.37</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45943.83333333334</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>2.7</v>
+        <v>3.81</v>
       </c>
       <c r="O11" t="n">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45943.83333333334</v>
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O12" t="n">
         <v>2.1</v>
@@ -1998,10 +1998,10 @@
         <v>3.21</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AA12" t="n">
         <v>3.5</v>

--- a/jogos_2025-10-13.xlsx
+++ b/jogos_2025-10-13.xlsx
@@ -652,20 +652,20 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -727,12 +727,12 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['10']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AG2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,109 +772,109 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="M3" t="n">
-        <v>3.82</v>
+        <v>3.35</v>
       </c>
       <c r="N3" t="n">
-        <v>5.12</v>
+        <v>3.1</v>
       </c>
       <c r="O3" t="n">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="P3" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.22</v>
+        <v>3.43</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>2.62</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>2.87</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45943.64583333334</v>
@@ -910,20 +910,20 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -985,7 +985,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23', '60']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,109 +1030,109 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>3.35</v>
+        <v>3.82</v>
       </c>
       <c r="N5" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S5" t="n">
         <v>3.1</v>
       </c>
-      <c r="O5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="T5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD5" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q5" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AE5" t="inlineStr">
         <is>
+          <t>['45+2']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.55</v>
+        <v>2.4</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45943.64583333334</v>
@@ -1168,20 +1168,20 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '88']</t>
         </is>
       </c>
       <c r="AG6" t="n">
@@ -1297,20 +1297,20 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['71']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AG7" t="n">
@@ -1426,20 +1426,20 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4', '18']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AG8" t="n">
@@ -1572,58 +1572,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="M9" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
-        <v>3.19</v>
+        <v>3.26</v>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S9" t="n">
         <v>2.44</v>
       </c>
       <c r="T9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="U9" t="n">
         <v>1.27</v>
       </c>
       <c r="V9" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="W9" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="X9" t="n">
         <v>2.56</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AB9" t="n">
         <v>1.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AD9" t="n">
         <v>1.75</v>
@@ -1642,7 +1642,7 @@
         <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AI9" t="n">
         <v>2.05</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="M10" t="n">
         <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="P10" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.26</v>
+        <v>3.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45943.83333333334</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="N11" t="n">
-        <v>3.81</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>2.62</v>
+        <v>2.86</v>
       </c>
       <c r="P11" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>2.1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>2.37</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45943.83333333334</v>
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="M12" t="n">
-        <v>3.29</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="O12" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q12" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="T12" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V12" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
-        <v>3.21</v>
+        <v>3.28</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AC12" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="AI12" t="n">
         <v>1.5</v>
